--- a/data/lista_desejos.xlsx
+++ b/data/lista_desejos.xlsx
@@ -465,40 +465,40 @@
         <v>365</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/Celular-Samsung-Galaxy-C%C3%A2mera-Qu%C3%A1drupla/dp/B0GKQTTCMM/ref=sr_1_4?dib=eyJ2IjoiMSJ9.vPSAC4pNHsg0gllOYcZZ8Zkuzt1yNFkcu2X_tMKNiB9rdWwRyMCyVdh7lIeGlIHbKGdOoSLb6CAEo6A0AWgUuJ5IDOBQnYIhJuKQIWiglZfC3TGNEtwYhpMbu9fmF_wYEO-1Pt0fkMDUvTsUCjUBwIufenBKSPtE_9cdDjA4VsoXwdr-kj1LcZ_vCrGSFXlJYsNqR0uebzA6iCMCyWThWzrY70kgLxkwEpRE4rcIPLfZgVaLeu5MUIsc7pCofVL9OhMLV12HiXnrT29hmssmRJvl-Y-s9199svaXSJwe6n8.GwDLQZm0nNpcnU0WPMNQqNDpKt7OHcqA_PyQxLi-A10&amp;dib_tag=se&amp;keywords=s26+ultra&amp;qid=1791500311&amp;sr=8-4&amp;ufe=app_do%3Aamzn1.fos.9e6a115c-05b9-4b96-8e1c-b1f9ce2ac1a6</t>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6930</v>
+        <v>140</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>140</v>
+        <v>6800</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
